--- a/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>012</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.334965</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.166909</v>
-      </c>
-      <c r="I2" t="n">
-        <v>173</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.334965</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.166909</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>163</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.334066</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.17276200000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>124</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.334066</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.172762</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>190</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.332661</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.170286</v>
-      </c>
-      <c r="I4" t="n">
-        <v>61</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.332661</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.170286</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>82081 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.335753</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.169732</v>
-      </c>
-      <c r="I5" t="n">
-        <v>468</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.335753</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.169732</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>82919</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.281868</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.083123</v>
-      </c>
-      <c r="I6" t="n">
-        <v>26</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.281868</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.083123</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>82952 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.335843</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.1661</v>
-      </c>
-      <c r="I7" t="n">
-        <v>426</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.335843</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.1661</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>83007 PATRON SAN MARCOS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.336823</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.170739</v>
-      </c>
-      <c r="I8" t="n">
-        <v>422</v>
-      </c>
-      <c r="J8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.336823</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.170739</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>SAN MARCOS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.335583</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.166876</v>
-      </c>
-      <c r="I9" t="n">
-        <v>821</v>
-      </c>
-      <c r="J9" t="n">
-        <v>62</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.335583</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.166876</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>24 DE JUNIO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-7.319073</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.173671</v>
-      </c>
-      <c r="I10" t="n">
-        <v>252</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-7.319073</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.173671</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>SAN MARCOS APOSTOL</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-7.33562</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.16981</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-7.33562</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.16981</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>1344</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-7.28201</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.08324</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-7.28201</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.08324</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>ALBERTO BUENO TIRADO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-7.33133</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.17155</v>
-      </c>
-      <c r="I13" t="n">
-        <v>307</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-7.33133</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.17155</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>JESUS DE NAZARET</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-7.33606</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.17001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-7.33606</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.17001</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>131275</t>
+          <t>778241</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>JESUS DE NAZARET</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.334965</t>
+          <t>-7.33606</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.166909</t>
+          <t>-78.17001</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>773601</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.334066</t>
+          <t>-7.28201</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.172762</t>
+          <t>-78.08324</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>819393</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>ALBERTO BUENO TIRADO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.332661</t>
+          <t>-7.33133</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.170286</t>
+          <t>-78.17155</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,42 +687,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>131402</t>
+          <t>131633</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82081 SAGRADO CORAZON DE JESUS</t>
+          <t>82919</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.335753</t>
+          <t>-7.281868</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.169732</t>
+          <t>-78.083123</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>131826</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>24 DE JUNIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.281868</t>
+          <t>-7.319073</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.083123</t>
+          <t>-78.173671</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>131652</t>
+          <t>131402</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>82952 DIVINO MAESTRO</t>
+          <t>82081 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.335843</t>
+          <t>-7.335753</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.1661</t>
+          <t>-78.169732</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>131770</t>
+          <t>131652</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>83007 PATRON SAN MARCOS</t>
+          <t>82952 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.336823</t>
+          <t>-7.335843</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.170739</t>
+          <t>-78.1661</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>426</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>131789</t>
+          <t>131770</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>83007 PATRON SAN MARCOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.335583</t>
+          <t>-7.336823</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.166876</t>
+          <t>-78.170739</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>422</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>131826</t>
+          <t>131336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24 DE JUNIO</t>
+          <t>190</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.319073</t>
+          <t>-7.332661</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.173671</t>
+          <t>-78.170286</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>773601</t>
+          <t>131317</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.28201</t>
+          <t>-7.334066</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.08324</t>
+          <t>-78.172762</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>124</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>819393</t>
+          <t>131789</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALBERTO BUENO TIRADO</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.33133</t>
+          <t>-7.335583</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.17155</t>
+          <t>-78.166876</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>821</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>778241</t>
+          <t>131275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARET</t>
+          <t>012</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.33606</t>
+          <t>-7.334965</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.17001</t>
+          <t>-78.166909</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>778241</t>
+          <t>819393</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARET</t>
+          <t>ALBERTO BUENO TIRADO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.33606</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.17001</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-7.33133</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-78.17155</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>773601</t>
+          <t>778241</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>JESUS DE NAZARET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.28201</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.08324</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-7.33606</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-78.17001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,42 +625,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>819393</t>
+          <t>773601</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALBERTO BUENO TIRADO</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.33133</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.17155</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-7.28201</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.08324</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>629864</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>SAN MARCOS APOSTOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.281868</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.083123</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-7.33562</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-78.16981</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,22 +759,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>-7.319073</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-78.173671</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>131402</t>
+          <t>131789</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>82081 SAGRADO CORAZON DE JESUS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.335753</t>
+          <t>821</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.169732</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-7.335583</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.166876</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>131652</t>
+          <t>131770</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>82952 DIVINO MAESTRO</t>
+          <t>83007 PATRON SAN MARCOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.335843</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.1661</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>-7.336823</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.170739</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>131770</t>
+          <t>131652</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>83007 PATRON SAN MARCOS</t>
+          <t>82952 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.336823</t>
+          <t>426</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.170739</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>-7.335843</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.1661</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>131633</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>82919</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.332661</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.170286</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-7.281868</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.083123</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>629864</t>
+          <t>131402</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN MARCOS APOSTOL</t>
+          <t>82081 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.33562</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.16981</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-7.335753</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.169732</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>131336</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>190</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.334066</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.172762</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>-7.332661</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.170286</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>131789</t>
+          <t>131317</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.335583</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.166876</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>-7.334066</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-78.172762</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-7.334965</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-78.166909</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
